--- a/demo/demo-data/sample-update-workbook.xlsx
+++ b/demo/demo-data/sample-update-workbook.xlsx
@@ -57,7 +57,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0;[Red]-#,##0.0;0.0"/>
     <numFmt numFmtId="170" formatCode="#,##0.00;[Red]-#,##0.00;0.00"/>
     <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="172" formatCode="#,##0,&quot;k&quot;;[Red]-#,##0,&quot;k&quot;;0"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0,&quot;k&quot;;[Red]-#,##0.0,&quot;k&quot;;0"/>
   </numFmts>
   <fonts count="27">
     <font>
